--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487993_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487993_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6605</v>
+        <v>7.4112</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1821</v>
+        <v>7.6519</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5215</v>
+        <v>-0.2407</v>
       </c>
       <c r="G2" t="n">
         <v>4.0325</v>
@@ -610,13 +610,13 @@
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.9844</v>
+        <v>-2.2337</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3617</v>
+        <v>-0.8918</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.6227</v>
+        <v>-1.3419</v>
       </c>
       <c r="V2" t="n">
         <v>4.2249</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4847</v>
+        <v>5.1958</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4027</v>
+        <v>6.0576</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.918</v>
+        <v>-0.8618</v>
       </c>
       <c r="G3" t="n">
         <v>6.567</v>
@@ -688,13 +688,13 @@
         <v>1.5858</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6086</v>
+        <v>-0.8975</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0658</v>
+        <v>-0.4109</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.4866</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8701</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0346</v>
+        <v>2.9429</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0113</v>
+        <v>0.4586</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0459</v>
+        <v>2.4843</v>
       </c>
       <c r="G4" t="n">
         <v>2.5974</v>
@@ -766,13 +766,13 @@
         <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9839</v>
+        <v>-1.0756</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1194</v>
+        <v>-0.6495</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1355</v>
+        <v>-0.4261</v>
       </c>
       <c r="V4" t="n">
         <v>2.6104</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3856</v>
+        <v>0.0323</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9932</v>
+        <v>-0.6875</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6075</v>
+        <v>0.7198</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2733</v>
@@ -922,13 +922,13 @@
         <v>0.1982</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3105</v>
+        <v>0.1074</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3744</v>
+        <v>-0.0688</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0638</v>
+        <v>0.1762</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.828</v>
+        <v>-0.2739</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5907</v>
+        <v>3.0606</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.4187</v>
+        <v>-3.3345</v>
       </c>
       <c r="G7" t="n">
         <v>2.7126</v>
@@ -1000,13 +1000,13 @@
         <v>0.9911</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9371</v>
+        <v>-1.383</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2369</v>
+        <v>-0.767</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7002</v>
+        <v>-0.616</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2071</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>P. GUINDO CASTILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,70 +1036,70 @@
         <v>-1.5045</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6387</v>
+        <v>-2.3578</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1342</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2894</v>
+        <v>-0.7507</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2441</v>
+        <v>-0.2475</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9547</v>
+        <v>-0.5031</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1896</v>
+        <v>-1.2979</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3179</v>
+        <v>0.0202</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1283</v>
+        <v>-1.3181</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9002</v>
+        <v>0.5472</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0738</v>
+        <v>-0.2677</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8264</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1982</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3876</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1893</v>
+        <v>0.5947</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6719000000000001</v>
+        <v>-0.0688</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7482</v>
+        <v>-0.0221</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9405</v>
+        <v>-0.2666</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. STRUKOV STRUKOV</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7678</v>
+        <v>-2.0596</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.58</v>
+        <v>-2.2499</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1878</v>
+        <v>0.1903</v>
       </c>
       <c r="G9" t="n">
-        <v>0.925</v>
+        <v>-0.2894</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0989</v>
+        <v>-1.2441</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0239</v>
+        <v>0.9547</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0041</v>
+        <v>-1.1896</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0487</v>
+        <v>-1.3179</v>
       </c>
       <c r="L9" t="n">
-        <v>1.0446</v>
+        <v>0.1283</v>
       </c>
       <c r="M9" t="n">
-        <v>0.929</v>
+        <v>0.9002</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0503</v>
+        <v>0.0738</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.8264</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.5858</v>
+        <v>-1.3876</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5858</v>
+        <v>1.1893</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7324000000000001</v>
+        <v>-0.6314</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4172</v>
+        <v>0.0607</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6848</v>
+        <v>-0.6921</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.4252</v>
+        <v>-0.9405</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.4074</v>
+        <v>0.2666</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.0178</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. GUINDO CASTILLO</t>
+          <t>V. STRUKOV STRUKOV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9225</v>
+        <v>-2.9517</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6634</v>
+        <v>-1.9043</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7409</v>
+        <v>-1.0474</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7507</v>
+        <v>0.925</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2475</v>
+        <v>-1.0989</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5031</v>
+        <v>2.0239</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2979</v>
+        <v>-0.0041</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0202</v>
+        <v>-1.0487</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3181</v>
+        <v>1.0446</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5472</v>
+        <v>0.929</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2677</v>
+        <v>-0.0503</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>-1.5858</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5947</v>
+        <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5088</v>
+        <v>-0.4515</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3744</v>
+        <v>0.0929</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1344</v>
+        <v>-0.5444</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2666</v>
+        <v>-3.4252</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.4074</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2666</v>
+        <v>-3.0178</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9521</v>
+        <v>-3.6612</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9047</v>
+        <v>-3.333</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0474</v>
+        <v>-0.3282</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6907</v>
@@ -1312,13 +1312,13 @@
         <v>1.784</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.986</v>
+        <v>-1.6951</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3727</v>
+        <v>-0.801</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6133</v>
+        <v>-0.8941</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4737</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.421999999999999</v>
+        <v>5.733999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>6.9869</v>
+        <v>7.298900000000001</v>
       </c>
       <c r="F12" t="n">
         <v>-1.5649</v>
@@ -1357,7 +1357,7 @@
         <v>15.4331</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.051299999999999</v>
+        <v>-8.051300000000001</v>
       </c>
       <c r="I12" t="n">
         <v>23.4846</v>
@@ -1372,7 +1372,7 @@
         <v>18.531</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3565000000000003</v>
+        <v>0.3565000000000002</v>
       </c>
       <c r="N12" t="n">
         <v>-4.5969</v>
@@ -1390,16 +1390,16 @@
         <v>11.8934</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.6632</v>
+        <v>-8.351199999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.8162</v>
+        <v>-3.5042</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.847099999999999</v>
+        <v>-4.8471</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.3479</v>
+        <v>-1.347900000000001</v>
       </c>
       <c r="W12" t="n">
         <v>7.6199</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.666499999999999</v>
+        <v>8.170199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>5.794</v>
+        <v>5.3865</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8725</v>
+        <v>2.7837</v>
       </c>
       <c r="G13" t="n">
         <v>1.6066</v>
@@ -1468,13 +1468,13 @@
         <v>2.3787</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3427</v>
+        <v>1.8464</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1566</v>
+        <v>0.7491</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1861</v>
+        <v>1.0973</v>
       </c>
       <c r="V13" t="n">
         <v>3.3296</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2706</v>
+        <v>4.3179</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4713</v>
+        <v>2.8601</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7994</v>
+        <v>1.4579</v>
       </c>
       <c r="G14" t="n">
         <v>0.6113</v>
@@ -1546,13 +1546,13 @@
         <v>2.1805</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6955</v>
+        <v>1.7427</v>
       </c>
       <c r="T14" t="n">
-        <v>1.23</v>
+        <v>0.6188</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4654</v>
+        <v>1.1239</v>
       </c>
       <c r="V14" t="n">
         <v>0.7746</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.375</v>
+        <v>0.3446</v>
       </c>
       <c r="E15" t="n">
-        <v>3.196</v>
+        <v>1.9736</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.821</v>
+        <v>-1.629</v>
       </c>
       <c r="G15" t="n">
         <v>-1.5785</v>
@@ -1624,13 +1624,13 @@
         <v>1.784</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9301</v>
+        <v>1.8997</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3973</v>
+        <v>1.1749</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.7248</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7695</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. MARTINEZ LAJARA</t>
+          <t>A. GUZMAN SALINAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1358</v>
+        <v>-1.187</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-1.7189</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1358</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.2971</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1.1664</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-1.4635</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.2051</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.6192</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.8243</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-0.092</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.5472</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.6392</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.784</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1358</v>
+        <v>0.3157</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.2525</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1358</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.5784</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6287</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8828</v>
+        <v>-2.0199</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1082</v>
+        <v>-1.4138</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7746</v>
+        <v>-0.6061</v>
       </c>
       <c r="G17" t="n">
         <v>-2.3623</v>
@@ -1780,13 +1780,13 @@
         <v>0.5947</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2834</v>
+        <v>1.1462</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9949</v>
+        <v>0.6893</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2885</v>
+        <v>0.4569</v>
       </c>
       <c r="V17" t="n">
         <v>-0.4074</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GUZMAN SALINAS</t>
+          <t>W. HASSAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0288</v>
+        <v>-2.5617</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2282</v>
+        <v>-1.7262</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1994</v>
+        <v>-0.8355</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2971</v>
+        <v>-3.7548</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1664</v>
+        <v>0.4828</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4635</v>
+        <v>-4.2376</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2051</v>
+        <v>-2.2931</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6192</v>
+        <v>0.343</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.8243</v>
+        <v>-2.6362</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.092</v>
+        <v>-1.4617</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5472</v>
+        <v>0.1398</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6392</v>
+        <v>-1.6014</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.784</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R18" t="n">
         <v>1.1893</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.526</v>
+        <v>0.1753</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2568</v>
+        <v>0.135</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2692</v>
+        <v>0.0403</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5784</v>
+        <v>1.8107</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2071</v>
+        <v>2.4142</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6287</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>N. KOROL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7095</v>
+        <v>-2.7727</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4265</v>
+        <v>-1.5303</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.136</v>
+        <v>-1.2424</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.162</v>
+        <v>-3.6627</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1378</v>
+        <v>0.0163</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0242</v>
+        <v>-3.679</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6308</v>
+        <v>-2.9615</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2775</v>
+        <v>-0.3292</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6467000000000001</v>
+        <v>-2.6323</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5312</v>
+        <v>-0.7012</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1398</v>
+        <v>0.3455</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.6709</v>
+        <v>-1.0467</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1982</v>
+        <v>0.5947</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1982</v>
+        <v>0.5947</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3909</v>
+        <v>0.5167</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0573</v>
+        <v>0.2241</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3336</v>
+        <v>0.2926</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1367</v>
+        <v>-0.2213</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1367</v>
+        <v>-1.4284</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W. HASSAN</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0711</v>
+        <v>-3.1451</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2355</v>
+        <v>0.019</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8355</v>
+        <v>-3.1641</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.7548</v>
+        <v>-3.162</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4828</v>
+        <v>-1.1378</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.2376</v>
+        <v>-2.0242</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.2931</v>
+        <v>-0.6308</v>
       </c>
       <c r="K20" t="n">
-        <v>0.343</v>
+        <v>-1.2775</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.6362</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4617</v>
+        <v>-2.5312</v>
       </c>
       <c r="N20" t="n">
         <v>0.1398</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6014</v>
+        <v>-2.6709</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1893</v>
+        <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.334</v>
+        <v>0.9553</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3744</v>
+        <v>0.6498</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0403</v>
+        <v>0.3055</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8107</v>
+        <v>-1.1367</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4142</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6036</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. KOROL</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0959</v>
+        <v>-5.889</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9378</v>
+        <v>-2.2851</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1582</v>
+        <v>-3.6038</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.6627</v>
+        <v>-2.8335</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0163</v>
+        <v>0.876</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.679</v>
+        <v>-3.7096</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.9615</v>
+        <v>0.3347</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3292</v>
+        <v>0.5926</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.6323</v>
+        <v>-0.2579</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7012</v>
+        <v>-3.1682</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3455</v>
+        <v>0.2834</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0467</v>
+        <v>-3.4517</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5947</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5947</v>
+        <v>1.784</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1934</v>
+        <v>0.7443</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1834</v>
+        <v>0.3535</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3768</v>
+        <v>0.3908</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2213</v>
+        <v>-2.6104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4284</v>
+        <v>-2.6104</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,144 +2125,66 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.8101</v>
+        <v>-4.7427</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8131</v>
+        <v>1.564900000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.9969</v>
+        <v>-6.307499999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.8335</v>
+        <v>-15.433</v>
       </c>
       <c r="H22" t="n">
-        <v>0.876</v>
+        <v>8.051500000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.7096</v>
+        <v>-23.4845</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3347</v>
+        <v>-0.3565000000000003</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5926</v>
+        <v>4.597</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2579</v>
+        <v>-4.953499999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.1682</v>
+        <v>-15.0765</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2834</v>
+        <v>3.4546</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.4517</v>
+        <v>-18.531</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1893</v>
+        <v>0.000100000000000211</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9733</v>
+        <v>-11.8932</v>
       </c>
       <c r="R22" t="n">
-        <v>1.784</v>
+        <v>11.8934</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1769</v>
+        <v>9.342299999999998</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1745</v>
+        <v>4.847</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0023</v>
+        <v>4.495299999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.6104</v>
+        <v>1.348</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>8.9678</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.6104</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>BYSPANIA TÍJOLA</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-5.421900000000001</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.564999999999999</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-6.986700000000001</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-15.433</v>
-      </c>
-      <c r="H23" t="n">
-        <v>8.051500000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-23.4845</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-0.3565000000000003</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4.597</v>
-      </c>
-      <c r="L23" t="n">
-        <v>-4.9535</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-15.0765</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.4546</v>
-      </c>
-      <c r="O23" t="n">
-        <v>-18.531</v>
-      </c>
-      <c r="P23" t="n">
-        <v>9.999999999998899e-05</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>-11.8932</v>
-      </c>
-      <c r="R23" t="n">
-        <v>11.8934</v>
-      </c>
-      <c r="S23" t="n">
-        <v>8.6633</v>
-      </c>
-      <c r="T23" t="n">
-        <v>4.847</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3.8162</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.348000000000001</v>
-      </c>
-      <c r="W23" t="n">
-        <v>8.9678</v>
-      </c>
-      <c r="X23" t="n">
         <v>-7.619899999999999</v>
       </c>
     </row>
